--- a/rapporten/prijsrapport-NL-2026-07-05.xlsx
+++ b/rapporten/prijsrapport-NL-2026-07-05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="246">
   <si>
     <t>Product</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Omerta - Royal X - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370260</t>
   </si>
   <si>
@@ -49,36 +52,63 @@
     <t>Koopjesfun.nl</t>
   </si>
   <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816813</t>
   </si>
   <si>
     <t>Minimarkt W&amp;M</t>
   </si>
   <si>
+    <t>Omerta - Night Out Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379239</t>
   </si>
   <si>
     <t>Bliksma Retail B.V.</t>
   </si>
   <si>
+    <t>Omerta - Daily Elegance Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379222</t>
   </si>
   <si>
+    <t>Omerta - Seduction Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379260</t>
   </si>
   <si>
+    <t>Omerta - Oud &amp; Class Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379307</t>
   </si>
   <si>
+    <t>Omerta - Night Power Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379284</t>
   </si>
   <si>
+    <t>Omerta - Wild energy Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379291</t>
   </si>
   <si>
+    <t>Colorful Shoe Shoe Pack</t>
+  </si>
+  <si>
     <t>8720938379253</t>
   </si>
   <si>
+    <t>Omerta - Signature Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379314</t>
   </si>
   <si>
@@ -88,6 +118,9 @@
     <t>8721055494126</t>
   </si>
   <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
     <t>6291012005082</t>
   </si>
   <si>
@@ -97,15 +130,27 @@
     <t>8721055493426</t>
   </si>
   <si>
+    <t>Creation Lamis My Spirit Eau de Parfum For Women 100ml</t>
+  </si>
+  <si>
     <t>6291012005648</t>
   </si>
   <si>
+    <t>Sentio Soft Suede Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8721055491453</t>
   </si>
   <si>
+    <t>Creation Lamis Pluton for men Eau de Toilette</t>
+  </si>
+  <si>
     <t>6291012005969</t>
   </si>
   <si>
+    <t>Omerta - Vanilla Fun - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658999447</t>
   </si>
   <si>
@@ -127,9 +172,15 @@
     <t>8721055493747</t>
   </si>
   <si>
+    <t>Sentio Rose Espresso Unisex Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8721055491415</t>
   </si>
   <si>
+    <t>NG Axure Sport Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214758325</t>
   </si>
   <si>
@@ -145,18 +196,33 @@
     <t>7640158816974</t>
   </si>
   <si>
+    <t>Real Time - Free Sky For Woman - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658002512</t>
   </si>
   <si>
+    <t>Omerta - Silver Ocean Blue - EDT men - 100 ml</t>
+  </si>
+  <si>
     <t>8715658370017</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Wonderful - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492733</t>
   </si>
   <si>
+    <t>Sentio Sway With Me Eau de Parfum For Her 50ml</t>
+  </si>
+  <si>
     <t>8721055491767</t>
   </si>
   <si>
+    <t>Sentio Parfum Universal For Woman Eau de Parfum for her 35ml</t>
+  </si>
+  <si>
     <t>7640158815816</t>
   </si>
   <si>
@@ -166,6 +232,9 @@
     <t>5414666010511</t>
   </si>
   <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
@@ -178,6 +247,9 @@
     <t>8721055492795</t>
   </si>
   <si>
+    <t>Sentio Attractive Life Geschenkset - 1 set</t>
+  </si>
+  <si>
     <t>7640158815557</t>
   </si>
   <si>
@@ -208,6 +280,9 @@
     <t>8721055491798</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492719</t>
   </si>
   <si>
@@ -229,6 +304,9 @@
     <t>8721055492726</t>
   </si>
   <si>
+    <t>Vibezz-Infusion Noir-Eau de Parfum For Her-100ml</t>
+  </si>
+  <si>
     <t>7640158819203</t>
   </si>
   <si>
@@ -250,6 +328,9 @@
     <t>8721055493082</t>
   </si>
   <si>
+    <t>Bubble Bliss Blooming Bella Parfum Giftbag - Eau de parfum voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055494300</t>
   </si>
   <si>
@@ -265,9 +346,15 @@
     <t>8715658009573</t>
   </si>
   <si>
+    <t>Hello Kitty Rainbow Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
     <t>8721055493297</t>
   </si>
   <si>
+    <t>Hello Kitty Kisses Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
     <t>8721055493273</t>
   </si>
   <si>
@@ -277,6 +364,9 @@
     <t>8719214752576</t>
   </si>
   <si>
+    <t>Omerta - Golden challenge EDT men 100 ml</t>
+  </si>
+  <si>
     <t>8720938379345</t>
   </si>
   <si>
@@ -286,69 +376,135 @@
     <t>8721055494218</t>
   </si>
   <si>
+    <t>Omerta - Sensible Man - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658999249</t>
   </si>
   <si>
+    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380658</t>
   </si>
   <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658999430</t>
   </si>
   <si>
+    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658370086</t>
   </si>
   <si>
+    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380665</t>
   </si>
   <si>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380931</t>
   </si>
   <si>
+    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380221</t>
   </si>
   <si>
+    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380672</t>
   </si>
   <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380115</t>
   </si>
   <si>
+    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8720938379352</t>
   </si>
   <si>
+    <t>Omerta - Royal X Red - EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370369</t>
   </si>
   <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
     <t>8715658380580</t>
   </si>
   <si>
+    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380351</t>
   </si>
   <si>
+    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658999638</t>
   </si>
   <si>
+    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380405</t>
   </si>
   <si>
+    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370543</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Elixer - 1EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370437</t>
   </si>
   <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658998839</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658997993</t>
   </si>
   <si>
+    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380757</t>
   </si>
   <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370505</t>
   </si>
   <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658370062</t>
   </si>
   <si>
@@ -358,6 +514,9 @@
     <t>7640158816899</t>
   </si>
   <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816790</t>
   </si>
   <si>
@@ -373,18 +532,33 @@
     <t>8721055493914</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494232</t>
   </si>
   <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816837</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494263</t>
   </si>
   <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816714</t>
   </si>
   <si>
@@ -394,45 +568,87 @@
     <t>8721055493181</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055493891</t>
   </si>
   <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493211</t>
   </si>
   <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055493884</t>
   </si>
   <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816653</t>
   </si>
   <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493198</t>
   </si>
   <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493228</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494225</t>
   </si>
   <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816691</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494270</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055493877</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055493853</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055493860</t>
   </si>
   <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816615</t>
   </si>
   <si>
@@ -442,6 +658,9 @@
     <t>8721055492245</t>
   </si>
   <si>
+    <t>Sentio Mary Davina Liora parfum - Eau de parfum spray voor dames - 100 ml</t>
+  </si>
+  <si>
     <t>8721055496656</t>
   </si>
   <si>
@@ -454,6 +673,9 @@
     <t>8721055492207</t>
   </si>
   <si>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>6291012000261</t>
   </si>
   <si>
@@ -469,12 +691,21 @@
     <t>8719214751203</t>
   </si>
   <si>
+    <t>Next Generation Classic Woman Elegance Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214753269</t>
   </si>
   <si>
+    <t>Sentio Mary Davina Cristal parfum - eau de parfum spray voor dames - 100 ml</t>
+  </si>
+  <si>
     <t>8721055496632</t>
   </si>
   <si>
+    <t>Sentio Love Van Love &amp; Casual Eau de Parfum 100 ml</t>
+  </si>
+  <si>
     <t>8721055499473</t>
   </si>
   <si>
@@ -494,6 +725,9 @@
   </si>
   <si>
     <t>8721055498131</t>
+  </si>
+  <si>
+    <t>De La Mare Parfum Raggio Di Sole 49 Caramel &amp; Pistachio Eau de Parfum 100 ml</t>
   </si>
   <si>
     <t>8721055498155</t>
@@ -950,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>11.5</v>
@@ -962,13 +1196,13 @@
         <v>1.51</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>9.99</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -976,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
         <v>11.5</v>
@@ -988,21 +1222,21 @@
         <v>1.51</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
         <v>11.5</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>5.25</v>
@@ -1014,21 +1248,21 @@
         <v>1.26</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
         <v>3.99</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>16.95</v>
@@ -1040,21 +1274,21 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1">
         <v>15.95</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>16.95</v>
@@ -1066,21 +1300,21 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
         <v>15.95</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>16.95</v>
@@ -1092,21 +1326,21 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
         <v>15.95</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>16.95</v>
@@ -1118,21 +1352,21 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
         <v>15.95</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>16.95</v>
@@ -1144,21 +1378,21 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
         <v>15.95</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>16.95</v>
@@ -1170,21 +1404,21 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1">
         <v>15.95</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1">
         <v>16.95</v>
@@ -1196,21 +1430,21 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1">
         <v>15.95</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>16.89</v>
@@ -1222,21 +1456,21 @@
         <v>0.94</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
         <v>15.95</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1">
         <v>14.95</v>
@@ -1248,21 +1482,21 @@
         <v>0.85</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
         <v>14.1</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1">
         <v>14.95</v>
@@ -1274,21 +1508,21 @@
         <v>0.85</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
         <v>14.1</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1">
         <v>14.95</v>
@@ -1300,21 +1534,21 @@
         <v>0.85</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
         <v>14.1</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1">
         <v>14.95</v>
@@ -1326,21 +1560,21 @@
         <v>0.85</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
         <v>14.1</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1">
         <v>14.95</v>
@@ -1352,21 +1586,21 @@
         <v>0.81</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
         <v>14.14</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1">
         <v>14.95</v>
@@ -1378,21 +1612,21 @@
         <v>0.78</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1">
         <v>14.17</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1">
         <v>14.95</v>
@@ -1404,21 +1638,21 @@
         <v>0.76</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="1">
         <v>14.19</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1">
         <v>14.95</v>
@@ -1430,21 +1664,21 @@
         <v>0.69</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
         <v>14.26</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1">
         <v>14.95</v>
@@ -1456,21 +1690,21 @@
         <v>0.69</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="1">
         <v>14.26</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1">
         <v>14.95</v>
@@ -1482,21 +1716,21 @@
         <v>0.69</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1">
         <v>14.26</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1">
         <v>14.95</v>
@@ -1508,21 +1742,21 @@
         <v>0.69</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
         <v>14.26</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1">
         <v>14.95</v>
@@ -1534,21 +1768,21 @@
         <v>0.69</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="1">
         <v>14.26</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1">
         <v>14.95</v>
@@ -1560,21 +1794,21 @@
         <v>0.68</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="1">
         <v>14.27</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1">
         <v>14.95</v>
@@ -1586,21 +1820,21 @@
         <v>0.68</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="1">
         <v>14.27</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1">
         <v>12.25</v>
@@ -1612,21 +1846,21 @@
         <v>0.56</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1">
         <v>11.69</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1">
         <v>10.49</v>
@@ -1638,21 +1872,21 @@
         <v>0.54</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1">
         <v>9.95</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1">
         <v>13.95</v>
@@ -1664,21 +1898,21 @@
         <v>0.54</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
         <v>13.41</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1">
         <v>13.95</v>
@@ -1690,21 +1924,21 @@
         <v>0.54</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="1">
         <v>13.41</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1">
         <v>11.99</v>
@@ -1716,21 +1950,21 @@
         <v>0.49</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
         <v>11.5</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1">
         <v>14.5</v>
@@ -1742,21 +1976,21 @@
         <v>0.49</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
         <v>14.01</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C33" s="1">
         <v>9.94</v>
@@ -1768,21 +2002,21 @@
         <v>0.46</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G33" s="1">
         <v>9.48</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C34" s="1">
         <v>11.95</v>
@@ -1794,21 +2028,21 @@
         <v>0.45</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" s="1">
         <v>11.5</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>11.95</v>
@@ -1820,21 +2054,21 @@
         <v>0.45</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G35" s="1">
         <v>11.5</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>13.95</v>
@@ -1846,21 +2080,21 @@
         <v>0.43</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1">
         <v>13.52</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>13.95</v>
@@ -1872,21 +2106,21 @@
         <v>0.43</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
         <v>13.52</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>13.95</v>
@@ -1898,21 +2132,21 @@
         <v>0.43</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
         <v>13.52</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>13.95</v>
@@ -1924,21 +2158,21 @@
         <v>0.43</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1">
         <v>13.52</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>13.95</v>
@@ -1950,21 +2184,21 @@
         <v>0.43</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40" s="1">
         <v>13.52</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>13.95</v>
@@ -1976,21 +2210,21 @@
         <v>0.39</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
         <v>13.56</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>13.95</v>
@@ -2002,21 +2236,21 @@
         <v>0.39</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
         <v>13.56</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>13.95</v>
@@ -2028,21 +2262,21 @@
         <v>0.39</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1">
         <v>13.56</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>13.95</v>
@@ -2054,21 +2288,21 @@
         <v>0.39</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" s="1">
         <v>13.56</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>21.95</v>
@@ -2080,21 +2314,21 @@
         <v>0.36</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45" s="1">
         <v>21.59</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1">
         <v>13.95</v>
@@ -2106,21 +2340,21 @@
         <v>0.36</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46" s="1">
         <v>13.59</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1">
         <v>13.95</v>
@@ -2132,21 +2366,21 @@
         <v>0.36</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1">
         <v>13.59</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1">
         <v>13.95</v>
@@ -2158,21 +2392,21 @@
         <v>0.36</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48" s="1">
         <v>13.59</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C49" s="1">
         <v>12.25</v>
@@ -2184,21 +2418,21 @@
         <v>0.36</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49" s="1">
         <v>11.89</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1">
         <v>12.25</v>
@@ -2210,21 +2444,21 @@
         <v>0.34</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" s="1">
         <v>11.91</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1">
         <v>13.95</v>
@@ -2236,21 +2470,21 @@
         <v>0.33</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1">
         <v>13.62</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1">
         <v>13.95</v>
@@ -2262,21 +2496,21 @@
         <v>0.31</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" s="1">
         <v>13.64</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1">
         <v>12.5</v>
@@ -2288,21 +2522,21 @@
         <v>0.3</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G53" s="1">
         <v>12.2</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1">
         <v>9.79</v>
@@ -2314,21 +2548,21 @@
         <v>0.29</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G54" s="1">
         <v>9.5</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1">
         <v>21.95</v>
@@ -2340,21 +2574,21 @@
         <v>0.29</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G55" s="1">
         <v>21.66</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C56" s="1">
         <v>9.79</v>
@@ -2366,21 +2600,21 @@
         <v>0.29</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G56" s="1">
         <v>9.5</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C57" s="1">
         <v>9.79</v>
@@ -2392,21 +2626,21 @@
         <v>0.29</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G57" s="1">
         <v>9.5</v>
       </c>
       <c r="H57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C58" s="1">
         <v>9.79</v>
@@ -2418,21 +2652,21 @@
         <v>0.29</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G58" s="1">
         <v>9.5</v>
       </c>
       <c r="H58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C59" s="1">
         <v>9.79</v>
@@ -2444,21 +2678,21 @@
         <v>0.29</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G59" s="1">
         <v>9.5</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C60" s="1">
         <v>9.79</v>
@@ -2470,21 +2704,21 @@
         <v>0.29</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G60" s="1">
         <v>9.5</v>
       </c>
       <c r="H60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C61" s="1">
         <v>9.79</v>
@@ -2496,21 +2730,21 @@
         <v>0.29</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G61" s="1">
         <v>9.5</v>
       </c>
       <c r="H61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="C62" s="1">
         <v>9.79</v>
@@ -2522,21 +2756,21 @@
         <v>0.29</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G62" s="1">
         <v>9.5</v>
       </c>
       <c r="H62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C63" s="1">
         <v>9.79</v>
@@ -2548,21 +2782,21 @@
         <v>0.29</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G63" s="1">
         <v>9.5</v>
       </c>
       <c r="H63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="C64" s="1">
         <v>9.79</v>
@@ -2574,21 +2808,21 @@
         <v>0.29</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G64" s="1">
         <v>9.5</v>
       </c>
       <c r="H64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1">
         <v>9.79</v>
@@ -2600,21 +2834,21 @@
         <v>0.29</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G65" s="1">
         <v>9.5</v>
       </c>
       <c r="H65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="C66" s="1">
         <v>9.79</v>
@@ -2626,21 +2860,21 @@
         <v>0.29</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G66" s="1">
         <v>9.5</v>
       </c>
       <c r="H66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="C67" s="1">
         <v>9.79</v>
@@ -2652,21 +2886,21 @@
         <v>0.29</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G67" s="1">
         <v>9.5</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C68" s="1">
         <v>9.79</v>
@@ -2678,21 +2912,21 @@
         <v>0.29</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G68" s="1">
         <v>9.5</v>
       </c>
       <c r="H68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="C69" s="1">
         <v>9.79</v>
@@ -2704,21 +2938,21 @@
         <v>0.29</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G69" s="1">
         <v>9.5</v>
       </c>
       <c r="H69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C70" s="1">
         <v>9.79</v>
@@ -2730,21 +2964,21 @@
         <v>0.29</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G70" s="1">
         <v>9.5</v>
       </c>
       <c r="H70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1">
         <v>9.79</v>
@@ -2756,21 +2990,21 @@
         <v>0.29</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G71" s="1">
         <v>9.5</v>
       </c>
       <c r="H71" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C72" s="1">
         <v>9.79</v>
@@ -2782,21 +3016,21 @@
         <v>0.29</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1">
         <v>9.5</v>
       </c>
       <c r="H72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="C73" s="1">
         <v>9.79</v>
@@ -2808,21 +3042,21 @@
         <v>0.29</v>
       </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G73" s="1">
         <v>9.5</v>
       </c>
       <c r="H73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C74" s="1">
         <v>9.79</v>
@@ -2834,21 +3068,21 @@
         <v>0.29</v>
       </c>
       <c r="F74" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G74" s="1">
         <v>9.5</v>
       </c>
       <c r="H74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C75" s="1">
         <v>9.79</v>
@@ -2860,21 +3094,21 @@
         <v>0.29</v>
       </c>
       <c r="F75" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G75" s="1">
         <v>9.5</v>
       </c>
       <c r="H75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="C76" s="1">
         <v>9.79</v>
@@ -2886,21 +3120,21 @@
         <v>0.29</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G76" s="1">
         <v>9.5</v>
       </c>
       <c r="H76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="C77" s="1">
         <v>9.79</v>
@@ -2912,21 +3146,21 @@
         <v>0.29</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G77" s="1">
         <v>9.5</v>
       </c>
       <c r="H77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="C78" s="1">
         <v>13.95</v>
@@ -2938,21 +3172,21 @@
         <v>0.27</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78" s="1">
         <v>13.68</v>
       </c>
       <c r="H78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="C79" s="1">
         <v>5.25</v>
@@ -2964,21 +3198,21 @@
         <v>0.26</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G79" s="1">
         <v>4.99</v>
       </c>
       <c r="H79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="C80" s="1">
         <v>13.95</v>
@@ -2990,21 +3224,21 @@
         <v>0.26</v>
       </c>
       <c r="F80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G80" s="1">
         <v>13.69</v>
       </c>
       <c r="H80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="C81" s="1">
         <v>21.95</v>
@@ -3016,21 +3250,21 @@
         <v>0.26</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G81" s="1">
         <v>21.69</v>
       </c>
       <c r="H81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="C82" s="1">
         <v>5.25</v>
@@ -3042,21 +3276,21 @@
         <v>0.26</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G82" s="1">
         <v>4.99</v>
       </c>
       <c r="H82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="C83" s="1">
         <v>5.25</v>
@@ -3068,21 +3302,21 @@
         <v>0.26</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G83" s="1">
         <v>4.99</v>
       </c>
       <c r="H83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="C84" s="1">
         <v>5.25</v>
@@ -3094,21 +3328,21 @@
         <v>0.26</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G84" s="1">
         <v>4.99</v>
       </c>
       <c r="H84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="C85" s="1">
         <v>5.25</v>
@@ -3120,21 +3354,21 @@
         <v>0.26</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G85" s="1">
         <v>4.99</v>
       </c>
       <c r="H85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="C86" s="1">
         <v>5.25</v>
@@ -3146,21 +3380,21 @@
         <v>0.26</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G86" s="1">
         <v>4.99</v>
       </c>
       <c r="H86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="C87" s="1">
         <v>21.95</v>
@@ -3172,21 +3406,21 @@
         <v>0.26</v>
       </c>
       <c r="F87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G87" s="1">
         <v>21.69</v>
       </c>
       <c r="H87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="C88" s="1">
         <v>5.25</v>
@@ -3198,21 +3432,21 @@
         <v>0.26</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G88" s="1">
         <v>4.99</v>
       </c>
       <c r="H88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="C89" s="1">
         <v>5.25</v>
@@ -3224,21 +3458,21 @@
         <v>0.26</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G89" s="1">
         <v>4.99</v>
       </c>
       <c r="H89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="C90" s="1">
         <v>5.25</v>
@@ -3250,21 +3484,21 @@
         <v>0.26</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G90" s="1">
         <v>4.99</v>
       </c>
       <c r="H90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="B91" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="C91" s="1">
         <v>5.25</v>
@@ -3276,21 +3510,21 @@
         <v>0.26</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G91" s="1">
         <v>4.99</v>
       </c>
       <c r="H91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="B92" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C92" s="1">
         <v>5.25</v>
@@ -3302,21 +3536,21 @@
         <v>0.26</v>
       </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G92" s="1">
         <v>4.99</v>
       </c>
       <c r="H92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="B93" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="C93" s="1">
         <v>5.25</v>
@@ -3328,21 +3562,21 @@
         <v>0.26</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G93" s="1">
         <v>4.99</v>
       </c>
       <c r="H93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="C94" s="1">
         <v>5.25</v>
@@ -3354,21 +3588,21 @@
         <v>0.26</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G94" s="1">
         <v>4.99</v>
       </c>
       <c r="H94" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="B95" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="C95" s="1">
         <v>5.25</v>
@@ -3380,21 +3614,21 @@
         <v>0.26</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G95" s="1">
         <v>4.99</v>
       </c>
       <c r="H95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="C96" s="1">
         <v>5.25</v>
@@ -3406,21 +3640,21 @@
         <v>0.26</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G96" s="1">
         <v>4.99</v>
       </c>
       <c r="H96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C97" s="1">
         <v>5.25</v>
@@ -3432,21 +3666,21 @@
         <v>0.26</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G97" s="1">
         <v>4.99</v>
       </c>
       <c r="H97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="C98" s="1">
         <v>5.25</v>
@@ -3458,21 +3692,21 @@
         <v>0.26</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G98" s="1">
         <v>4.99</v>
       </c>
       <c r="H98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="C99" s="1">
         <v>5.25</v>
@@ -3484,21 +3718,21 @@
         <v>0.26</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G99" s="1">
         <v>4.99</v>
       </c>
       <c r="H99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="C100" s="1">
         <v>5.25</v>
@@ -3510,21 +3744,21 @@
         <v>0.26</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G100" s="1">
         <v>4.99</v>
       </c>
       <c r="H100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="C101" s="1">
         <v>5.25</v>
@@ -3536,21 +3770,21 @@
         <v>0.26</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G101" s="1">
         <v>4.99</v>
       </c>
       <c r="H101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="B102" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="C102" s="1">
         <v>13.95</v>
@@ -3562,21 +3796,21 @@
         <v>0.25</v>
       </c>
       <c r="F102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G102" s="1">
         <v>13.7</v>
       </c>
       <c r="H102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="B103" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="C103" s="1">
         <v>9.25</v>
@@ -3588,21 +3822,21 @@
         <v>0.25</v>
       </c>
       <c r="F103" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
       </c>
       <c r="H103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="C104" s="1">
         <v>13.95</v>
@@ -3614,21 +3848,21 @@
         <v>0.25</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G104" s="1">
         <v>13.7</v>
       </c>
       <c r="H104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="C105" s="1">
         <v>8.75</v>
@@ -3640,21 +3874,21 @@
         <v>0.25</v>
       </c>
       <c r="F105" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G105" s="1">
         <v>8.5</v>
       </c>
       <c r="H105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="C106" s="1">
         <v>12.5</v>
@@ -3666,21 +3900,21 @@
         <v>0.24</v>
       </c>
       <c r="F106" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G106" s="1">
         <v>12.26</v>
       </c>
       <c r="H106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="B107" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="C107" s="1">
         <v>12.5</v>
@@ -3692,21 +3926,21 @@
         <v>0.23</v>
       </c>
       <c r="F107" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G107" s="1">
         <v>12.27</v>
       </c>
       <c r="H107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="B108" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="C108" s="1">
         <v>9.19</v>
@@ -3718,21 +3952,21 @@
         <v>0.19</v>
       </c>
       <c r="F108" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G108" s="1">
         <v>9</v>
       </c>
       <c r="H108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="C109" s="1">
         <v>9.19</v>
@@ -3744,21 +3978,21 @@
         <v>0.19</v>
       </c>
       <c r="F109" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G109" s="1">
         <v>9</v>
       </c>
       <c r="H109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B110" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="C110" s="1">
         <v>9.19</v>
@@ -3770,21 +4004,21 @@
         <v>0.19</v>
       </c>
       <c r="F110" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G110" s="1">
         <v>9</v>
       </c>
       <c r="H110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="B111" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="C111" s="1">
         <v>21.95</v>
@@ -3796,21 +4030,21 @@
         <v>0.18</v>
       </c>
       <c r="F111" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G111" s="1">
         <v>21.77</v>
       </c>
       <c r="H111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>235</v>
       </c>
       <c r="C112" s="1">
         <v>14.95</v>
@@ -3822,21 +4056,21 @@
         <v>0.15</v>
       </c>
       <c r="F112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G112" s="1">
         <v>14.8</v>
       </c>
       <c r="H112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>236</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="C113" s="1">
         <v>14.95</v>
@@ -3848,21 +4082,21 @@
         <v>0.11</v>
       </c>
       <c r="F113" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G113" s="1">
         <v>14.84</v>
       </c>
       <c r="H113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="B114" t="s">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="C114" s="1">
         <v>14.95</v>
@@ -3874,21 +4108,21 @@
         <v>0.1</v>
       </c>
       <c r="F114" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G114" s="1">
         <v>14.85</v>
       </c>
       <c r="H114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="C115" s="1">
         <v>12.29</v>
@@ -3900,21 +4134,21 @@
         <v>0.1</v>
       </c>
       <c r="F115" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="G115" s="1">
         <v>12.19</v>
       </c>
       <c r="H115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="C116" s="1">
         <v>12.5</v>
@@ -3926,13 +4160,13 @@
         <v>0</v>
       </c>
       <c r="F116" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="G116" s="1">
         <v>12.5</v>
       </c>
       <c r="H116" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
